--- a/LLM_Extraction_and_CrossCritique/interactive-table/results/pipeline_comparison_p2_vs_p3.xlsx
+++ b/LLM_Extraction_and_CrossCritique/interactive-table/results/pipeline_comparison_p2_vs_p3.xlsx
@@ -822,10 +822,10 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.6999999999999998</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="F2">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -854,10 +854,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.6</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="F3">
-        <v>0.6666666666666666</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -886,10 +886,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.7333333333333334</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0.8148148148148149</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -918,10 +918,10 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F5">
-        <v>0.6666666666666666</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="G5">
         <v>0.3333333333333333</v>
@@ -944,16 +944,16 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E6">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F6">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G6">
         <v>0.1666666666666667</v>
@@ -982,10 +982,10 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0.6</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="F7">
-        <v>0.6666666666666666</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G7">
         <v>0.5</v>
@@ -1008,10 +1008,10 @@
         <v>16</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E8">
         <v>0.4000000000000001</v>
@@ -1040,13 +1040,13 @@
         <v>17</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <v>0.8571428571428571</v>
@@ -1072,13 +1072,13 @@
         <v>18</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E10">
-        <v>0.6</v>
+        <v>0.7714285714285714</v>
       </c>
       <c r="F10">
         <v>0.8571428571428571</v>
@@ -1104,13 +1104,13 @@
         <v>19</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>0.5555555555555556</v>
+        <v>1</v>
       </c>
       <c r="F11">
         <v>0.8333333333333334</v>
@@ -1142,10 +1142,10 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0.6999999999999998</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F12">
-        <v>0.875</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1174,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F13">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1206,10 +1206,10 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="F14">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1238,10 +1238,10 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0.5333333333333333</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F15">
-        <v>0.6666666666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1270,10 +1270,10 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="F16">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G16">
         <v>0.5</v>
@@ -1296,13 +1296,13 @@
         <v>25</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E17">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="F17">
         <v>0.8333333333333334</v>
@@ -1328,10 +1328,10 @@
         <v>26</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E18">
         <v>0.6</v>
@@ -1360,16 +1360,16 @@
         <v>27</v>
       </c>
       <c r="C19">
-        <v>0.2</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D19">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E19">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F19">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1392,16 +1392,16 @@
         <v>28</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E20">
-        <v>0.6999999999999998</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F20">
-        <v>0.875</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1424,16 +1424,16 @@
         <v>29</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E21">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F21">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="G21">
         <v>0.6666666666666666</v>
@@ -1456,16 +1456,16 @@
         <v>30</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E22">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F22">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G22">
         <v>0.6666666666666666</v>
@@ -1494,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0.6999999999999998</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="F23">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G23">
         <v>0.75</v>
@@ -1526,10 +1526,10 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>0.6999999999999998</v>
+        <v>0.7047619047619048</v>
       </c>
       <c r="F24">
-        <v>0.875</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1552,16 +1552,16 @@
         <v>33</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F25">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1584,10 +1584,10 @@
         <v>34</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E26">
         <v>0.6</v>
@@ -1616,16 +1616,16 @@
         <v>35</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F27">
-        <v>0.75</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -1654,10 +1654,10 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>0.5</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F28">
-        <v>0.625</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -1680,16 +1680,16 @@
         <v>37</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <v>0.5</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F29">
-        <v>0.625</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -1712,16 +1712,16 @@
         <v>38</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E30">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F30">
-        <v>0.625</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -1744,16 +1744,16 @@
         <v>39</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>0.5</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F31">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -1776,16 +1776,16 @@
         <v>40</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F32">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -1808,16 +1808,16 @@
         <v>41</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F33">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -1840,10 +1840,10 @@
         <v>42</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E34">
         <v>0.6</v>
@@ -1872,16 +1872,16 @@
         <v>43</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E35">
-        <v>0.6</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F35">
-        <v>0.75</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -1910,7 +1910,7 @@
         <v>0</v>
       </c>
       <c r="E36">
-        <v>0.6</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="F36">
         <v>0.75</v>
@@ -1936,16 +1936,16 @@
         <v>45</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F37">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -1974,10 +1974,10 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>0.6999999999999998</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F38">
-        <v>0.875</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -2000,16 +2000,16 @@
         <v>47</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>0.6</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F39">
-        <v>0.75</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2032,16 +2032,16 @@
         <v>48</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40">
-        <v>0.5</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F40">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -2064,16 +2064,16 @@
         <v>49</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41">
-        <v>0.6</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F41">
-        <v>0.75</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -2096,16 +2096,16 @@
         <v>50</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F42">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -2128,16 +2128,16 @@
         <v>51</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43">
-        <v>0.5</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F43">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2160,16 +2160,16 @@
         <v>52</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44">
-        <v>0.5</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="F44">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -2192,16 +2192,16 @@
         <v>53</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E45">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="F45">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2224,16 +2224,16 @@
         <v>54</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E46">
-        <v>0.7259259259259259</v>
+        <v>0.5</v>
       </c>
       <c r="F46">
-        <v>0.875</v>
+        <v>0.625</v>
       </c>
       <c r="G46">
         <v>0.5</v>
@@ -2256,16 +2256,16 @@
         <v>55</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F47">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -2288,16 +2288,16 @@
         <v>56</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F48">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -2320,16 +2320,16 @@
         <v>57</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49">
         <v>0.6666666666666666</v>
       </c>
       <c r="F49">
-        <v>0.75</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -2352,16 +2352,16 @@
         <v>58</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F50">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -2390,10 +2390,10 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F51">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -2416,16 +2416,16 @@
         <v>60</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52">
-        <v>0.6666666666666666</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F52">
-        <v>0.75</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -2448,16 +2448,16 @@
         <v>61</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53">
         <v>0.6666666666666666</v>
       </c>
       <c r="F53">
-        <v>0.75</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -2480,16 +2480,16 @@
         <v>62</v>
       </c>
       <c r="C54">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E54">
-        <v>0.6999999999999998</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F54">
-        <v>0.875</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -2544,16 +2544,16 @@
         <v>64</v>
       </c>
       <c r="C56">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="F56">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -2576,16 +2576,16 @@
         <v>65</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E57">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F57">
-        <v>0.75</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -2646,10 +2646,10 @@
         <v>0</v>
       </c>
       <c r="E59">
-        <v>0.6666666666666666</v>
+        <v>0.6</v>
       </c>
       <c r="F59">
-        <v>0.8333333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -2672,16 +2672,16 @@
         <v>68</v>
       </c>
       <c r="C60">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E60">
-        <v>0.6</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="F60">
-        <v>0.8571428571428571</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -2704,16 +2704,16 @@
         <v>69</v>
       </c>
       <c r="C61">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E61">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F61">
-        <v>0.8571428571428571</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -2742,7 +2742,7 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0.5555555555555556</v>
+        <v>0.5</v>
       </c>
       <c r="F62">
         <v>0.5555555555555556</v>
@@ -2768,13 +2768,13 @@
         <v>71</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63">
-        <v>0.6</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="F63">
         <v>0.8571428571428571</v>
@@ -2800,13 +2800,13 @@
         <v>72</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64">
-        <v>0.6</v>
+        <v>0.8214285714285715</v>
       </c>
       <c r="F64">
         <v>0.8571428571428571</v>
@@ -2838,10 +2838,10 @@
         <v>1</v>
       </c>
       <c r="E65">
-        <v>0.6</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F65">
-        <v>0.75</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -2864,16 +2864,16 @@
         <v>74</v>
       </c>
       <c r="C66">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D66">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E66">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="F66">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G66">
         <v>0.6666666666666666</v>
@@ -2896,10 +2896,10 @@
         <v>75</v>
       </c>
       <c r="C67">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E67">
         <v>0.6</v>
@@ -2928,16 +2928,16 @@
         <v>76</v>
       </c>
       <c r="C68">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E68">
-        <v>0.6</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="F68">
-        <v>0.8571428571428571</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -2960,10 +2960,10 @@
         <v>77</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E69">
         <v>0.5</v>
@@ -2992,13 +2992,13 @@
         <v>78</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E70">
-        <v>0.5</v>
+        <v>0.5185185185185185</v>
       </c>
       <c r="F70">
         <v>0.8333333333333334</v>
@@ -3056,13 +3056,13 @@
         <v>80</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72">
-        <v>0.5</v>
+        <v>0.5370370370370371</v>
       </c>
       <c r="F72">
         <v>0.8333333333333334</v>
@@ -3094,10 +3094,10 @@
         <v>1</v>
       </c>
       <c r="E73">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F73">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -3126,10 +3126,10 @@
         <v>1</v>
       </c>
       <c r="E74">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F74">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -3152,16 +3152,16 @@
         <v>83</v>
       </c>
       <c r="C75">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E75">
-        <v>0.6</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="F75">
-        <v>0.8571428571428571</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -3190,10 +3190,10 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="F76">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -3222,10 +3222,10 @@
         <v>0</v>
       </c>
       <c r="E77">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="F77">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -3254,10 +3254,10 @@
         <v>0</v>
       </c>
       <c r="E78">
-        <v>0.7259259259259259</v>
+        <v>0.6</v>
       </c>
       <c r="F78">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -3286,7 +3286,7 @@
         <v>0</v>
       </c>
       <c r="E79">
-        <v>0.7259259259259259</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F79">
         <v>0.875</v>
@@ -3376,10 +3376,10 @@
         <v>90</v>
       </c>
       <c r="C82">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D82">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E82">
         <v>0.6999999999999998</v>
@@ -3446,10 +3446,10 @@
         <v>0</v>
       </c>
       <c r="E84">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F84">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G84">
         <v>1</v>
@@ -3472,16 +3472,16 @@
         <v>93</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F85">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -3504,16 +3504,16 @@
         <v>94</v>
       </c>
       <c r="C86">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D86">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E86">
-        <v>0.6999999999999998</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F86">
-        <v>0.875</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G86">
         <v>0.5</v>
@@ -3542,10 +3542,10 @@
         <v>0</v>
       </c>
       <c r="E87">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F87">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -3568,16 +3568,16 @@
         <v>96</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F88">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G88">
         <v>0.6666666666666666</v>
@@ -3606,10 +3606,10 @@
         <v>0</v>
       </c>
       <c r="E89">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="F89">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G89">
         <v>0.5</v>
@@ -3638,10 +3638,10 @@
         <v>0</v>
       </c>
       <c r="E90">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F90">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -3699,13 +3699,13 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="D92">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E92">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F92">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -3760,16 +3760,16 @@
         <v>102</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D94">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E94">
-        <v>0.6</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F94">
-        <v>0.75</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G94">
         <v>0.5</v>
@@ -3792,16 +3792,16 @@
         <v>103</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>0.2777777777777777</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E95">
-        <v>0.6</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F95">
-        <v>0.75</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -3824,16 +3824,16 @@
         <v>104</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E96">
-        <v>0.6</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F96">
-        <v>0.75</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -3856,10 +3856,10 @@
         <v>105</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97">
         <v>0.6</v>
@@ -3888,10 +3888,10 @@
         <v>106</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E98">
         <v>0.6</v>
@@ -3920,16 +3920,16 @@
         <v>107</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F99">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -3952,7 +3952,7 @@
         <v>108</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -3984,13 +3984,13 @@
         <v>109</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E101">
-        <v>0.5185185185185185</v>
+        <v>0.5</v>
       </c>
       <c r="F101">
         <v>0.8333333333333334</v>
@@ -4131,19 +4131,19 @@
         <v>116</v>
       </c>
       <c r="B2">
-        <v>0.1336666666666667</v>
+        <v>0.355111111111111</v>
       </c>
       <c r="C2">
         <v>0.6825</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4151,19 +4151,19 @@
         <v>117</v>
       </c>
       <c r="B3">
-        <v>0.1475</v>
+        <v>0.3808333333333334</v>
       </c>
       <c r="C3">
         <v>0.68</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E3">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4171,19 +4171,19 @@
         <v>118</v>
       </c>
       <c r="B4">
-        <v>0.6144074074074074</v>
+        <v>0.6511865079365079</v>
       </c>
       <c r="C4">
         <v>0.5686666666666667</v>
       </c>
       <c r="D4">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="E4">
         <v>14</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4191,19 +4191,19 @@
         <v>119</v>
       </c>
       <c r="B5">
-        <v>0.7806481481481481</v>
+        <v>0.8038624338624338</v>
       </c>
       <c r="C5">
         <v>0.7214682539682538</v>
       </c>
       <c r="D5">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -4244,22 +4244,22 @@
         <v>116</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D2">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E2">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4267,22 +4267,22 @@
         <v>117</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D3">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E3">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4290,10 +4290,10 @@
         <v>118</v>
       </c>
       <c r="B4">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D4">
         <v>14</v>
@@ -4302,10 +4302,10 @@
         <v>14</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>53</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4313,22 +4313,22 @@
         <v>119</v>
       </c>
       <c r="B5">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C5">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
